--- a/dashboard/assets/notas/acesso-2025.xlsx
+++ b/dashboard/assets/notas/acesso-2025.xlsx
@@ -1,278 +1,43 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>Microsoft Excel</Application>
-  <DocSecurity>0</DocSecurity>
-  <ScaleCrop>false</ScaleCrop>
-  <HeadingPairs>
-    <vt:vector size="2" baseType="variant">
-      <vt:variant>
-        <vt:lpstr>Planilhas</vt:lpstr>
-      </vt:variant>
-      <vt:variant>
-        <vt:i4>7</vt:i4>
-      </vt:variant>
-    </vt:vector>
-  </HeadingPairs>
-  <TitlesOfParts>
-    <vt:vector size="7" baseType="lpstr">
-      <vt:lpstr>TOTAL</vt:lpstr>
-      <vt:lpstr>COREOGRAFIA</vt:lpstr>
-      <vt:lpstr>MARCAÇÃO</vt:lpstr>
-      <vt:lpstr>ANIMAÇÃO</vt:lpstr>
-      <vt:lpstr>FIGURINO</vt:lpstr>
-      <vt:lpstr>CASAL DE NOIVOS</vt:lpstr>
-      <vt:lpstr>TRILHA SONORA</vt:lpstr>
-    </vt:vector>
-  </TitlesOfParts>
-  <LinksUpToDate>false</LinksUpToDate>
-  <SharedDoc>false</SharedDoc>
-  <HyperlinksChanged>false</HyperlinksChanged>
-  <AppVersion>16.0300</AppVersion>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tiago\Documents\GitHub\site-linq-dfe-beta\dashboard\assets\notas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{B91CEC3C-2277-43EC-87E8-E0647345D95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="TOTAL" sheetId="19" r:id="rId1"/>
+    <sheet name="COREOGRAFIA" sheetId="26" r:id="rId2"/>
+    <sheet name="MARCAÇÃO" sheetId="27" r:id="rId3"/>
+    <sheet name="ANIMAÇÃO" sheetId="28" r:id="rId4"/>
+    <sheet name="FIGURINO" sheetId="29" r:id="rId5"/>
+    <sheet name="CASAL DE NOIVOS" sheetId="30" r:id="rId6"/>
+    <sheet name="TRILHA SONORA" sheetId="31" r:id="rId7"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <cp:lastModifiedBy>Tiago</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-12T21:40:55Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-15T11:02:51Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="2" name="Created">
-    <vt:filetime>2026-02-02T00:00:00Z</vt:filetime>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="3" name="Creator">
-    <vt:lpwstr>www.smallpdf.com</vt:lpwstr>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="4" name="LastSaved">
-    <vt:filetime>2026-03-12T00:00:00Z</vt:filetime>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="5" name="Producer">
-    <vt:lpwstr>www.smallpdf.com</vt:lpwstr>
-  </property>
-</Properties>
-</file>
-
-<file path=xl\calcChain.xml><?xml version="1.0" encoding="utf-8"?>
-<calcChain xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <c r="E11" i="31" l="1"/>
-  <c r="F11" i="31" s="1"/>
-  <c r="G11" i="31" s="1"/>
-  <c r="E10" i="31"/>
-  <c r="F10" i="31" s="1"/>
-  <c r="G10" i="31" s="1"/>
-  <c r="E9" i="31"/>
-  <c r="F9" i="31" s="1"/>
-  <c r="G9" i="31" s="1"/>
-  <c r="E8" i="31"/>
-  <c r="F8" i="31" s="1"/>
-  <c r="G8" i="31" s="1"/>
-  <c r="E7" i="31"/>
-  <c r="F7" i="31" s="1"/>
-  <c r="G7" i="31" s="1"/>
-  <c r="E6" i="31"/>
-  <c r="F6" i="31" s="1"/>
-  <c r="G6" i="31" s="1"/>
-  <c r="E5" i="31"/>
-  <c r="F5" i="31" s="1"/>
-  <c r="G5" i="31" s="1"/>
-  <c r="E4" i="31"/>
-  <c r="F4" i="31" s="1"/>
-  <c r="G4" i="31" s="1"/>
-  <c r="E3" i="31"/>
-  <c r="F3" i="31" s="1"/>
-  <c r="G3" i="31" s="1"/>
-  <c r="E2" i="31"/>
-  <c r="F2" i="31" s="1"/>
-  <c r="G2" i="31" s="1"/>
-  <c r="E11" i="30"/>
-  <c r="F11" i="30" s="1"/>
-  <c r="G11" i="30" s="1"/>
-  <c r="E10" i="30"/>
-  <c r="F10" i="30" s="1"/>
-  <c r="G10" i="30" s="1"/>
-  <c r="E9" i="30"/>
-  <c r="F9" i="30" s="1"/>
-  <c r="G9" i="30" s="1"/>
-  <c r="E8" i="30"/>
-  <c r="F8" i="30" s="1"/>
-  <c r="G8" i="30" s="1"/>
-  <c r="E7" i="30"/>
-  <c r="F7" i="30" s="1"/>
-  <c r="G7" i="30" s="1"/>
-  <c r="E6" i="30"/>
-  <c r="F6" i="30" s="1"/>
-  <c r="G6" i="30" s="1"/>
-  <c r="E5" i="30"/>
-  <c r="F5" i="30" s="1"/>
-  <c r="G5" i="30" s="1"/>
-  <c r="E4" i="30"/>
-  <c r="F4" i="30" s="1"/>
-  <c r="G4" i="30" s="1"/>
-  <c r="E3" i="30"/>
-  <c r="F3" i="30" s="1"/>
-  <c r="G3" i="30" s="1"/>
-  <c r="E2" i="30"/>
-  <c r="F2" i="30" s="1"/>
-  <c r="G2" i="30" s="1"/>
-  <c r="E11" i="29"/>
-  <c r="F11" i="29" s="1"/>
-  <c r="G11" i="29" s="1"/>
-  <c r="E10" i="29"/>
-  <c r="F10" i="29" s="1"/>
-  <c r="G10" i="29" s="1"/>
-  <c r="E9" i="29"/>
-  <c r="F9" i="29" s="1"/>
-  <c r="G9" i="29" s="1"/>
-  <c r="E8" i="29"/>
-  <c r="F8" i="29" s="1"/>
-  <c r="G8" i="29" s="1"/>
-  <c r="E7" i="29"/>
-  <c r="F7" i="29" s="1"/>
-  <c r="G7" i="29" s="1"/>
-  <c r="E6" i="29"/>
-  <c r="F6" i="29" s="1"/>
-  <c r="G6" i="29" s="1"/>
-  <c r="E5" i="29"/>
-  <c r="F5" i="29" s="1"/>
-  <c r="G5" i="29" s="1"/>
-  <c r="E4" i="29"/>
-  <c r="F4" i="29" s="1"/>
-  <c r="G4" i="29" s="1"/>
-  <c r="E3" i="29"/>
-  <c r="F3" i="29" s="1"/>
-  <c r="G3" i="29" s="1"/>
-  <c r="E2" i="29"/>
-  <c r="F2" i="29" s="1"/>
-  <c r="G2" i="29" s="1"/>
-  <c r="E11" i="28"/>
-  <c r="F11" i="28" s="1"/>
-  <c r="G11" i="28" s="1"/>
-  <c r="E10" i="28"/>
-  <c r="F10" i="28" s="1"/>
-  <c r="G10" i="28" s="1"/>
-  <c r="E9" i="28"/>
-  <c r="F9" i="28" s="1"/>
-  <c r="G9" i="28" s="1"/>
-  <c r="E8" i="28"/>
-  <c r="F8" i="28" s="1"/>
-  <c r="G8" i="28" s="1"/>
-  <c r="E7" i="28"/>
-  <c r="F7" i="28" s="1"/>
-  <c r="G7" i="28" s="1"/>
-  <c r="E6" i="28"/>
-  <c r="F6" i="28" s="1"/>
-  <c r="G6" i="28" s="1"/>
-  <c r="E5" i="28"/>
-  <c r="F5" i="28" s="1"/>
-  <c r="G5" i="28" s="1"/>
-  <c r="E4" i="28"/>
-  <c r="F4" i="28" s="1"/>
-  <c r="G4" i="28" s="1"/>
-  <c r="E3" i="28"/>
-  <c r="F3" i="28" s="1"/>
-  <c r="G3" i="28" s="1"/>
-  <c r="E2" i="28"/>
-  <c r="F2" i="28" s="1"/>
-  <c r="G2" i="28" s="1"/>
-  <c r="E11" i="27"/>
-  <c r="F11" i="27" s="1"/>
-  <c r="G11" i="27" s="1"/>
-  <c r="E10" i="27"/>
-  <c r="F10" i="27" s="1"/>
-  <c r="G10" i="27" s="1"/>
-  <c r="E9" i="27"/>
-  <c r="F9" i="27" s="1"/>
-  <c r="G9" i="27" s="1"/>
-  <c r="E8" i="27"/>
-  <c r="F8" i="27" s="1"/>
-  <c r="G8" i="27" s="1"/>
-  <c r="E7" i="27"/>
-  <c r="F7" i="27" s="1"/>
-  <c r="G7" i="27" s="1"/>
-  <c r="E6" i="27"/>
-  <c r="F6" i="27" s="1"/>
-  <c r="G6" i="27" s="1"/>
-  <c r="E5" i="27"/>
-  <c r="F5" i="27" s="1"/>
-  <c r="G5" i="27" s="1"/>
-  <c r="E4" i="27"/>
-  <c r="F4" i="27" s="1"/>
-  <c r="G4" i="27" s="1"/>
-  <c r="E3" i="27"/>
-  <c r="F3" i="27" s="1"/>
-  <c r="G3" i="27" s="1"/>
-  <c r="E2" i="27"/>
-  <c r="F2" i="27" s="1"/>
-  <c r="G2" i="27" s="1"/>
-  <c r="G3" i="26"/>
-  <c r="G4" i="26"/>
-  <c r="G5" i="26"/>
-  <c r="G6" i="26"/>
-  <c r="G7" i="26"/>
-  <c r="G8" i="26"/>
-  <c r="G9" i="26"/>
-  <c r="G10" i="26"/>
-  <c r="G11" i="26"/>
-  <c r="G2" i="26"/>
-  <c r="F4" i="26"/>
-  <c r="F3" i="26"/>
-  <c r="F5" i="26"/>
-  <c r="F6" i="26"/>
-  <c r="F7" i="26"/>
-  <c r="F8" i="26"/>
-  <c r="F9" i="26"/>
-  <c r="F10" i="26"/>
-  <c r="F11" i="26"/>
-  <c r="F2" i="26"/>
-  <c r="E3" i="26"/>
-  <c r="E4" i="26"/>
-  <c r="E5" i="26"/>
-  <c r="E6" i="26"/>
-  <c r="E7" i="26"/>
-  <c r="E8" i="26"/>
-  <c r="E9" i="26"/>
-  <c r="E10" i="26"/>
-  <c r="E11" i="26"/>
-  <c r="E2" i="26"/>
-  <c r="I3" i="19"/>
-  <c r="I4" i="19"/>
-  <c r="I5" i="19"/>
-  <c r="I6" i="19"/>
-  <c r="I7" i="19"/>
-  <c r="I8" i="19"/>
-  <c r="I9" i="19"/>
-  <c r="I10" i="19"/>
-  <c r="I11" i="19"/>
-  <c r="I2" i="19"/>
-  <c r="H3" i="19"/>
-  <c r="H4" i="19"/>
-  <c r="H5" i="19"/>
-  <c r="H6" i="19"/>
-  <c r="H7" i="19"/>
-  <c r="H8" i="19"/>
-  <c r="H9" i="19"/>
-  <c r="H10" i="19"/>
-  <c r="H11" i="19"/>
-  <c r="H2" i="19"/>
-  <c r="G11" i="19"/>
-  <c r="G3" i="19"/>
-  <c r="G4" i="19"/>
-  <c r="G5" i="19"/>
-  <c r="G6" i="19"/>
-  <c r="G7" i="19"/>
-  <c r="G8" i="19"/>
-  <c r="G9" i="19"/>
-  <c r="G10" i="19"/>
-  <c r="G2" i="19"/>
-</calcChain>
-</file>
-
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="27">
   <si>
     <r>
@@ -498,7 +263,7 @@
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
@@ -621,7 +386,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -679,9 +444,6 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
@@ -711,7 +473,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -1030,44 +792,7 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tiago\Documents\GitHub\fantasy-junino\assets\notas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A72CA70-6EC3-47F5-9EF3-14FD66620143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="TOTAL" sheetId="19" r:id="rId1"/>
-    <sheet name="COREOGRAFIA" sheetId="26" r:id="rId2"/>
-    <sheet name="MARCAÇÃO" sheetId="27" r:id="rId3"/>
-    <sheet name="ANIMAÇÃO" sheetId="28" r:id="rId4"/>
-    <sheet name="FIGURINO" sheetId="29" r:id="rId5"/>
-    <sheet name="CASAL DE NOIVOS" sheetId="30" r:id="rId6"/>
-    <sheet name="TRILHA SONORA" sheetId="31" r:id="rId7"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -1121,13 +846,16 @@
         <v>537.6</v>
       </c>
       <c r="G2">
-        <f>F2/COUNTIF(C2:E2,"&lt;&gt;0")</f>
+        <f t="shared" ref="G2:G11" si="0">F2/COUNTIF(C2:E2,"&lt;&gt;0")</f>
+        <v>179.20000000000002</v>
       </c>
       <c r="H2">
-        <f>G2/6</f>
+        <f t="shared" ref="H2:H11" si="1">G2/6</f>
+        <v>29.866666666666671</v>
       </c>
       <c r="I2">
-        <f>H2/3</f>
+        <f t="shared" ref="I2:I11" si="2">H2/3</f>
+        <v>9.9555555555555575</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -1150,13 +878,16 @@
         <v>535.6</v>
       </c>
       <c r="G3">
-        <f>F3/COUNTIF(C3:E3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>178.53333333333333</v>
       </c>
       <c r="H3">
-        <f>G3/6</f>
+        <f t="shared" si="1"/>
+        <v>29.755555555555556</v>
       </c>
       <c r="I3">
-        <f>H3/3</f>
+        <f t="shared" si="2"/>
+        <v>9.9185185185185194</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -1179,13 +910,16 @@
         <v>535.4</v>
       </c>
       <c r="G4">
-        <f>F4/COUNTIF(C4:E4,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>178.46666666666667</v>
       </c>
       <c r="H4">
-        <f>G4/6</f>
+        <f t="shared" si="1"/>
+        <v>29.744444444444444</v>
       </c>
       <c r="I4">
-        <f>H4/3</f>
+        <f t="shared" si="2"/>
+        <v>9.9148148148148145</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -1208,13 +942,16 @@
         <v>533.79999999999995</v>
       </c>
       <c r="G5">
-        <f>F5/COUNTIF(C5:E5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>177.93333333333331</v>
       </c>
       <c r="H5">
-        <f>G5/6</f>
+        <f t="shared" si="1"/>
+        <v>29.655555555555551</v>
       </c>
       <c r="I5">
-        <f>H5/3</f>
+        <f t="shared" si="2"/>
+        <v>9.8851851851851844</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -1237,13 +974,16 @@
         <v>531.9</v>
       </c>
       <c r="G6">
-        <f>F6/COUNTIF(C6:E6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>177.29999999999998</v>
       </c>
       <c r="H6">
-        <f>G6/6</f>
+        <f t="shared" si="1"/>
+        <v>29.549999999999997</v>
       </c>
       <c r="I6">
-        <f>H6/3</f>
+        <f t="shared" si="2"/>
+        <v>9.85</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -1266,13 +1006,16 @@
         <v>531.79999999999995</v>
       </c>
       <c r="G7">
-        <f>F7/COUNTIF(C7:E7,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>177.26666666666665</v>
       </c>
       <c r="H7">
-        <f>G7/6</f>
+        <f t="shared" si="1"/>
+        <v>29.544444444444441</v>
       </c>
       <c r="I7">
-        <f>H7/3</f>
+        <f t="shared" si="2"/>
+        <v>9.8481481481481463</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -1295,13 +1038,16 @@
         <v>531</v>
       </c>
       <c r="G8">
-        <f>F8/COUNTIF(C8:E8,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>177</v>
       </c>
       <c r="H8">
-        <f>G8/6</f>
+        <f t="shared" si="1"/>
+        <v>29.5</v>
       </c>
       <c r="I8">
-        <f>H8/3</f>
+        <f t="shared" si="2"/>
+        <v>9.8333333333333339</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -1324,13 +1070,16 @@
         <v>528.9</v>
       </c>
       <c r="G9">
-        <f>F9/COUNTIF(C9:E9,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>176.29999999999998</v>
       </c>
       <c r="H9">
-        <f>G9/6</f>
+        <f t="shared" si="1"/>
+        <v>29.383333333333329</v>
       </c>
       <c r="I9">
-        <f>H9/3</f>
+        <f t="shared" si="2"/>
+        <v>9.7944444444444425</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -1353,13 +1102,16 @@
         <v>526.70000000000005</v>
       </c>
       <c r="G10">
-        <f>F10/COUNTIF(C10:E10,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>175.56666666666669</v>
       </c>
       <c r="H10">
-        <f>G10/6</f>
+        <f t="shared" si="1"/>
+        <v>29.261111111111116</v>
       </c>
       <c r="I10">
-        <f>H10/3</f>
+        <f t="shared" si="2"/>
+        <v>9.7537037037037049</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -1382,13 +1134,16 @@
         <v>345.4</v>
       </c>
       <c r="G11">
-        <f>F11/COUNTIF(C11:E11,"&lt;&gt;0")</f>
+        <f>F11/2</f>
+        <v>172.7</v>
       </c>
       <c r="H11">
-        <f>G11/6</f>
+        <f t="shared" si="1"/>
+        <v>28.783333333333331</v>
       </c>
       <c r="I11">
-        <f>H11/3</f>
+        <f t="shared" si="2"/>
+        <v>9.5944444444444432</v>
       </c>
     </row>
   </sheetData>
@@ -1397,9 +1152,9 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{876C352C-DD0F-4759-952B-15AC060EF592}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="34.83203125" defaultRowHeight="18.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.1640625" style="16" bestFit="1" customWidth="1"/>
@@ -1436,240 +1191,260 @@
       <c r="A2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="19">
         <v>29.5</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="19">
         <v>29.9</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="19">
         <v>29.3</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="20">
         <f>SUM(B2:D2)</f>
         <v>88.7</v>
       </c>
       <c r="F2">
-        <f>E2/COUNTIF(B2:D2,"&lt;&gt;0")</f>
+        <f t="shared" ref="F2:F11" si="0">E2/COUNTIF(B2:D2,"&lt;&gt;0")</f>
+        <v>29.566666666666666</v>
       </c>
       <c r="G2">
-        <f>F2/3</f>
+        <f t="shared" ref="G2:G11" si="1">F2/3</f>
+        <v>9.8555555555555561</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <v>28.9</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="19">
         <v>29.3</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="19">
         <v>29.1</v>
       </c>
-      <c r="E3" s="21">
-        <f t="shared" ref="E3:E11" si="0">SUM(B3:D3)</f>
+      <c r="E3" s="20">
+        <f t="shared" ref="E3:E11" si="2">SUM(B3:D3)</f>
         <v>87.300000000000011</v>
       </c>
       <c r="F3">
-        <f>E3/COUNTIF(B3:D3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.100000000000005</v>
       </c>
       <c r="G3">
-        <f>F3/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7000000000000011</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="19">
         <v>28.3</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="19">
         <v>28.5</v>
       </c>
-      <c r="E4" s="21">
-        <f t="shared" si="0"/>
+      <c r="E4" s="20">
+        <f t="shared" si="2"/>
         <v>56.8</v>
       </c>
       <c r="F4">
-        <f>E4/COUNTIF(B4:D4,"&lt;&gt;0")</f>
+        <f>E4/2</f>
+        <v>28.4</v>
       </c>
       <c r="G4">
-        <f>F4/3</f>
+        <f t="shared" si="1"/>
+        <v>9.4666666666666668</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="19">
         <v>29.5</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="19">
         <v>29.6</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="19">
         <v>29.6</v>
       </c>
-      <c r="E5" s="21">
-        <f t="shared" si="0"/>
+      <c r="E5" s="20">
+        <f t="shared" si="2"/>
         <v>88.7</v>
       </c>
       <c r="F5">
-        <f>E5/COUNTIF(B5:D5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.566666666666666</v>
       </c>
       <c r="G5">
-        <f>F5/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8555555555555561</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="19">
         <v>29</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="19">
         <v>29.6</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="19">
         <v>29.3</v>
       </c>
-      <c r="E6" s="21">
-        <f t="shared" si="0"/>
+      <c r="E6" s="20">
+        <f t="shared" si="2"/>
         <v>87.9</v>
       </c>
       <c r="F6">
-        <f>E6/COUNTIF(B6:D6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.3</v>
       </c>
       <c r="G6">
-        <f>F6/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7666666666666675</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="19">
         <v>29.3</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="19">
         <v>29.8</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="19">
         <v>28.9</v>
       </c>
-      <c r="E7" s="21">
-        <f t="shared" si="0"/>
+      <c r="E7" s="20">
+        <f t="shared" si="2"/>
         <v>88</v>
       </c>
       <c r="F7">
-        <f>E7/COUNTIF(B7:D7,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.333333333333332</v>
       </c>
       <c r="G7">
-        <f>F7/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7777777777777768</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="19">
         <v>29.1</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="22">
         <v>29.2</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="19">
         <v>28.5</v>
       </c>
-      <c r="E8" s="21">
-        <f t="shared" si="0"/>
+      <c r="E8" s="20">
+        <f t="shared" si="2"/>
         <v>86.8</v>
       </c>
       <c r="F8">
-        <f>E8/COUNTIF(B8:D8,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>28.933333333333334</v>
       </c>
       <c r="G8">
-        <f>F8/3</f>
+        <f t="shared" si="1"/>
+        <v>9.6444444444444439</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="19">
         <v>28.8</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="19">
         <v>29.3</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="19">
         <v>28.6</v>
       </c>
-      <c r="E9" s="21">
-        <f t="shared" si="0"/>
+      <c r="E9" s="20">
+        <f t="shared" si="2"/>
         <v>86.7</v>
       </c>
       <c r="F9">
-        <f>E9/COUNTIF(B9:D9,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>28.900000000000002</v>
       </c>
       <c r="G9">
-        <f>F9/3</f>
+        <f t="shared" si="1"/>
+        <v>9.6333333333333346</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="19">
         <v>29</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="19">
         <v>29.7</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="19">
         <v>29.1</v>
       </c>
-      <c r="E10" s="21">
-        <f t="shared" si="0"/>
+      <c r="E10" s="20">
+        <f t="shared" si="2"/>
         <v>87.800000000000011</v>
       </c>
       <c r="F10">
-        <f>E10/COUNTIF(B10:D10,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.266666666666669</v>
       </c>
       <c r="G10">
-        <f>F10/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7555555555555564</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="19">
         <v>29.3</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="19">
         <v>29.2</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="19">
         <v>29.8</v>
       </c>
-      <c r="E11" s="21">
-        <f t="shared" si="0"/>
+      <c r="E11" s="20">
+        <f t="shared" si="2"/>
         <v>88.3</v>
       </c>
       <c r="F11">
-        <f>E11/COUNTIF(B11:D11,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.433333333333334</v>
       </c>
       <c r="G11">
-        <f>F11/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8111111111111118</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -1681,25 +1456,16 @@
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
       <c r="H20" s="17"/>
-      <c r="F20">
-        <f>E20/COUNTIF(B20:D20,"&lt;&gt;0")</f>
-      </c>
-      <c r="G20">
-        <f>F20/3</f>
-      </c>
-    </row>
-    <row r="33" s="16" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="34" s="16" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="35" s="16" customFormat="1" x14ac:dyDescent="0.2"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C15A1B-79A1-4943-8014-F4C16CEE14A3}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="34.83203125" defaultRowHeight="18.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.1640625" style="16" bestFit="1" customWidth="1"/>
@@ -1736,240 +1502,260 @@
       <c r="A2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="19">
         <v>29.4</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="19">
         <v>29.8</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="19">
         <v>29.4</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="20">
         <f>SUM(B2:D2)</f>
         <v>88.6</v>
       </c>
       <c r="F2">
-        <f>E2/COUNTIF(B2:D2,"&lt;&gt;0")</f>
+        <f t="shared" ref="F2:F11" si="0">E2/COUNTIF(B2:D2,"&lt;&gt;0")</f>
+        <v>29.533333333333331</v>
       </c>
       <c r="G2">
-        <f>F2/3</f>
+        <f t="shared" ref="G2:G11" si="1">F2/3</f>
+        <v>9.8444444444444432</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <v>29.3</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="19">
         <v>29.2</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="19">
         <v>29.4</v>
       </c>
-      <c r="E3" s="21">
-        <f t="shared" ref="E3:E11" si="0">SUM(B3:D3)</f>
+      <c r="E3" s="20">
+        <f t="shared" ref="E3:E11" si="2">SUM(B3:D3)</f>
         <v>87.9</v>
       </c>
       <c r="F3">
-        <f>E3/COUNTIF(B3:D3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.3</v>
       </c>
       <c r="G3">
-        <f>F3/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7666666666666675</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="19">
         <v>28.6</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="19">
         <v>28.9</v>
       </c>
-      <c r="E4" s="21">
-        <f t="shared" si="0"/>
+      <c r="E4" s="20">
+        <f t="shared" si="2"/>
         <v>57.5</v>
       </c>
       <c r="F4">
-        <f>E4/COUNTIF(B4:D4,"&lt;&gt;0")</f>
+        <f>E4/2</f>
+        <v>28.75</v>
       </c>
       <c r="G4">
-        <f>F4/3</f>
+        <f t="shared" si="1"/>
+        <v>9.5833333333333339</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="19">
         <v>29.8</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="19">
         <v>29.9</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="19">
         <v>30</v>
       </c>
-      <c r="E5" s="21">
-        <f t="shared" si="0"/>
+      <c r="E5" s="20">
+        <f t="shared" si="2"/>
         <v>89.7</v>
       </c>
       <c r="F5">
-        <f>E5/COUNTIF(B5:D5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.900000000000002</v>
       </c>
       <c r="G5">
-        <f>F5/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9666666666666668</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="19">
         <v>29.6</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="19">
         <v>29.9</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="19">
         <v>29.8</v>
       </c>
-      <c r="E6" s="21">
-        <f t="shared" si="0"/>
+      <c r="E6" s="20">
+        <f t="shared" si="2"/>
         <v>89.3</v>
       </c>
       <c r="F6">
-        <f>E6/COUNTIF(B6:D6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.766666666666666</v>
       </c>
       <c r="G6">
-        <f>F6/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9222222222222225</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="19">
         <v>29.7</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="19">
         <v>29.6</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="19">
         <v>29.5</v>
       </c>
-      <c r="E7" s="21">
-        <f t="shared" si="0"/>
+      <c r="E7" s="20">
+        <f t="shared" si="2"/>
         <v>88.8</v>
       </c>
       <c r="F7">
-        <f>E7/COUNTIF(B7:D7,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.599999999999998</v>
       </c>
       <c r="G7">
-        <f>F7/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8666666666666654</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="19">
         <v>29.4</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="22">
         <v>29.8</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="19">
         <v>29.3</v>
       </c>
-      <c r="E8" s="21">
-        <f t="shared" si="0"/>
+      <c r="E8" s="20">
+        <f t="shared" si="2"/>
         <v>88.5</v>
       </c>
       <c r="F8">
-        <f>E8/COUNTIF(B8:D8,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.5</v>
       </c>
       <c r="G8">
-        <f>F8/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8333333333333339</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="19">
         <v>28.9</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="19">
         <v>29.4</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="19">
         <v>29.2</v>
       </c>
-      <c r="E9" s="21">
-        <f t="shared" si="0"/>
+      <c r="E9" s="20">
+        <f t="shared" si="2"/>
         <v>87.5</v>
       </c>
       <c r="F9">
-        <f>E9/COUNTIF(B9:D9,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.166666666666668</v>
       </c>
       <c r="G9">
-        <f>F9/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7222222222222232</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="19">
         <v>28.8</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="19">
         <v>29.3</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="19">
         <v>29</v>
       </c>
-      <c r="E10" s="21">
-        <f t="shared" si="0"/>
+      <c r="E10" s="20">
+        <f t="shared" si="2"/>
         <v>87.1</v>
       </c>
       <c r="F10">
-        <f>E10/COUNTIF(B10:D10,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.033333333333331</v>
       </c>
       <c r="G10">
-        <f>F10/3</f>
+        <f t="shared" si="1"/>
+        <v>9.6777777777777771</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="19">
         <v>29.8</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="19">
         <v>29.8</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="19">
         <v>29.9</v>
       </c>
-      <c r="E11" s="21">
-        <f t="shared" si="0"/>
+      <c r="E11" s="20">
+        <f t="shared" si="2"/>
         <v>89.5</v>
       </c>
       <c r="F11">
-        <f>E11/COUNTIF(B11:D11,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.833333333333332</v>
       </c>
       <c r="G11">
-        <f>F11/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9444444444444446</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -1981,24 +1767,15 @@
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
       <c r="H20" s="17"/>
-      <c r="F20">
-        <f>E20/COUNTIF(B20:D20,"&lt;&gt;0")</f>
-      </c>
-      <c r="G20">
-        <f>F20/3</f>
-      </c>
-    </row>
-    <row r="33" s="16" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="34" s="16" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="35" s="16" customFormat="1" x14ac:dyDescent="0.2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02010D3F-B0FA-4F68-B1A8-490746D57296}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="34.83203125" defaultRowHeight="18.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.1640625" style="16" bestFit="1" customWidth="1"/>
@@ -2035,240 +1812,260 @@
       <c r="A2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="19">
         <v>29.9</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="19">
         <v>30</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="19">
         <v>29.9</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="20">
         <f>SUM(B2:D2)</f>
         <v>89.8</v>
       </c>
       <c r="F2">
-        <f>E2/COUNTIF(B2:D2,"&lt;&gt;0")</f>
+        <f t="shared" ref="F2:F11" si="0">E2/COUNTIF(B2:D2,"&lt;&gt;0")</f>
+        <v>29.933333333333334</v>
       </c>
       <c r="G2">
-        <f>F2/3</f>
+        <f t="shared" ref="G2:G11" si="1">F2/3</f>
+        <v>9.9777777777777779</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <v>29.6</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="19">
         <v>29.7</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="19">
         <v>29.8</v>
       </c>
-      <c r="E3" s="21">
-        <f t="shared" ref="E3:E11" si="0">SUM(B3:D3)</f>
+      <c r="E3" s="20">
+        <f t="shared" ref="E3:E11" si="2">SUM(B3:D3)</f>
         <v>89.1</v>
       </c>
       <c r="F3">
-        <f>E3/COUNTIF(B3:D3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.7</v>
       </c>
       <c r="G3">
-        <f>F3/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="19">
         <v>28.8</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="19">
         <v>28.9</v>
       </c>
-      <c r="E4" s="21">
-        <f t="shared" si="0"/>
+      <c r="E4" s="20">
+        <f t="shared" si="2"/>
         <v>57.7</v>
       </c>
       <c r="F4">
-        <f>E4/COUNTIF(B4:D4,"&lt;&gt;0")</f>
+        <f>E4/2</f>
+        <v>28.85</v>
       </c>
       <c r="G4">
-        <f>F4/3</f>
+        <f t="shared" si="1"/>
+        <v>9.6166666666666671</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="19">
         <v>30</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="19">
         <v>29.7</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="19">
         <v>30</v>
       </c>
-      <c r="E5" s="21">
-        <f t="shared" si="0"/>
+      <c r="E5" s="20">
+        <f t="shared" si="2"/>
         <v>89.7</v>
       </c>
       <c r="F5">
-        <f>E5/COUNTIF(B5:D5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.900000000000002</v>
       </c>
       <c r="G5">
-        <f>F5/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9666666666666668</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="19">
         <v>29.2</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="19">
         <v>29.5</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="19">
         <v>29.3</v>
       </c>
-      <c r="E6" s="21">
-        <f t="shared" si="0"/>
+      <c r="E6" s="20">
+        <f t="shared" si="2"/>
         <v>88</v>
       </c>
       <c r="F6">
-        <f>E6/COUNTIF(B6:D6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.333333333333332</v>
       </c>
       <c r="G6">
-        <f>F6/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7777777777777768</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="19">
         <v>29.8</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="19">
         <v>29.5</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="19">
         <v>29.5</v>
       </c>
-      <c r="E7" s="21">
-        <f t="shared" si="0"/>
+      <c r="E7" s="20">
+        <f t="shared" si="2"/>
         <v>88.8</v>
       </c>
       <c r="F7">
-        <f>E7/COUNTIF(B7:D7,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.599999999999998</v>
       </c>
       <c r="G7">
-        <f>F7/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8666666666666654</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="19">
         <v>29.4</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="22">
         <v>29.3</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="19">
         <v>29</v>
       </c>
-      <c r="E8" s="21">
-        <f t="shared" si="0"/>
+      <c r="E8" s="20">
+        <f t="shared" si="2"/>
         <v>87.7</v>
       </c>
       <c r="F8">
-        <f>E8/COUNTIF(B8:D8,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.233333333333334</v>
       </c>
       <c r="G8">
-        <f>F8/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7444444444444454</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="19">
         <v>29.2</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="19">
         <v>29.2</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="19">
         <v>29</v>
       </c>
-      <c r="E9" s="21">
-        <f t="shared" si="0"/>
+      <c r="E9" s="20">
+        <f t="shared" si="2"/>
         <v>87.4</v>
       </c>
       <c r="F9">
-        <f>E9/COUNTIF(B9:D9,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.133333333333336</v>
       </c>
       <c r="G9">
-        <f>F9/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7111111111111121</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="19">
         <v>29.9</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="19">
         <v>29.6</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="19">
         <v>29.3</v>
       </c>
-      <c r="E10" s="21">
-        <f t="shared" si="0"/>
+      <c r="E10" s="20">
+        <f t="shared" si="2"/>
         <v>88.8</v>
       </c>
       <c r="F10">
-        <f>E10/COUNTIF(B10:D10,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.599999999999998</v>
       </c>
       <c r="G10">
-        <f>F10/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8666666666666654</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="19">
         <v>30</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="19">
         <v>29.4</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="19">
         <v>30</v>
       </c>
-      <c r="E11" s="21">
-        <f t="shared" si="0"/>
+      <c r="E11" s="20">
+        <f t="shared" si="2"/>
         <v>89.4</v>
       </c>
       <c r="F11">
-        <f>E11/COUNTIF(B11:D11,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.8</v>
       </c>
       <c r="G11">
-        <f>F11/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9333333333333336</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -2280,24 +2077,15 @@
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
       <c r="H20" s="17"/>
-      <c r="F20">
-        <f>E20/COUNTIF(B20:D20,"&lt;&gt;0")</f>
-      </c>
-      <c r="G20">
-        <f>F20/3</f>
-      </c>
-    </row>
-    <row r="33" s="16" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="34" s="16" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="35" s="16" customFormat="1" x14ac:dyDescent="0.2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33870F86-ACC3-47BF-A9F6-93904C2D9367}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="34.83203125" defaultRowHeight="18.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.1640625" style="16" bestFit="1" customWidth="1"/>
@@ -2334,240 +2122,260 @@
       <c r="A2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="19">
         <v>30</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="19">
         <v>30</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="19">
         <v>29.6</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="20">
         <f>SUM(B2:D2)</f>
         <v>89.6</v>
       </c>
       <c r="F2">
-        <f>E2/COUNTIF(B2:D2,"&lt;&gt;0")</f>
+        <f t="shared" ref="F2:F11" si="0">E2/COUNTIF(B2:D2,"&lt;&gt;0")</f>
+        <v>29.866666666666664</v>
       </c>
       <c r="G2">
-        <f>F2/3</f>
+        <f t="shared" ref="G2:G11" si="1">F2/3</f>
+        <v>9.9555555555555539</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <v>29.8</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="19">
         <v>30</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="19">
         <v>29.5</v>
       </c>
-      <c r="E3" s="21">
-        <f t="shared" ref="E3:E11" si="0">SUM(B3:D3)</f>
+      <c r="E3" s="20">
+        <f t="shared" ref="E3:E11" si="2">SUM(B3:D3)</f>
         <v>89.3</v>
       </c>
       <c r="F3">
-        <f>E3/COUNTIF(B3:D3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.766666666666666</v>
       </c>
       <c r="G3">
-        <f>F3/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9222222222222225</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="19">
         <v>28.5</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="19">
         <v>28.6</v>
       </c>
-      <c r="E4" s="21">
-        <f t="shared" si="0"/>
+      <c r="E4" s="20">
+        <f t="shared" si="2"/>
         <v>57.1</v>
       </c>
       <c r="F4">
-        <f>E4/COUNTIF(B4:D4,"&lt;&gt;0")</f>
+        <f>E4/2</f>
+        <v>28.55</v>
       </c>
       <c r="G4">
-        <f>F4/3</f>
+        <f t="shared" si="1"/>
+        <v>9.5166666666666675</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="19">
         <v>30</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="19">
         <v>30</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="19">
         <v>30</v>
       </c>
-      <c r="E5" s="21">
-        <f t="shared" si="0"/>
+      <c r="E5" s="20">
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="F5">
-        <f>E5/COUNTIF(B5:D5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="G5">
-        <f>F5/3</f>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="19">
         <v>29.8</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="19">
         <v>29.8</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="19">
         <v>29.8</v>
       </c>
-      <c r="E6" s="21">
-        <f t="shared" si="0"/>
+      <c r="E6" s="20">
+        <f t="shared" si="2"/>
         <v>89.4</v>
       </c>
       <c r="F6">
-        <f>E6/COUNTIF(B6:D6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.8</v>
       </c>
       <c r="G6">
-        <f>F6/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9333333333333336</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="19">
         <v>29.9</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="19">
         <v>29.9</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="19">
         <v>29.6</v>
       </c>
-      <c r="E7" s="21">
-        <f t="shared" si="0"/>
+      <c r="E7" s="20">
+        <f t="shared" si="2"/>
         <v>89.4</v>
       </c>
       <c r="F7">
-        <f>E7/COUNTIF(B7:D7,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.8</v>
       </c>
       <c r="G7">
-        <f>F7/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9333333333333336</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="19">
         <v>29.7</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="22">
         <v>29.8</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="19">
         <v>29.2</v>
       </c>
-      <c r="E8" s="21">
-        <f t="shared" si="0"/>
+      <c r="E8" s="20">
+        <f t="shared" si="2"/>
         <v>88.7</v>
       </c>
       <c r="F8">
-        <f>E8/COUNTIF(B8:D8,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.566666666666666</v>
       </c>
       <c r="G8">
-        <f>F8/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8555555555555561</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="19">
         <v>29.4</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="19">
         <v>29.6</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="19">
         <v>29.2</v>
       </c>
-      <c r="E9" s="21">
-        <f t="shared" si="0"/>
+      <c r="E9" s="20">
+        <f t="shared" si="2"/>
         <v>88.2</v>
       </c>
       <c r="F9">
-        <f>E9/COUNTIF(B9:D9,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.400000000000002</v>
       </c>
       <c r="G9">
-        <f>F9/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8000000000000007</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="19">
         <v>29.8</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="19">
         <v>29.8</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="19">
         <v>29.5</v>
       </c>
-      <c r="E10" s="21">
-        <f t="shared" si="0"/>
+      <c r="E10" s="20">
+        <f t="shared" si="2"/>
         <v>89.1</v>
       </c>
       <c r="F10">
-        <f>E10/COUNTIF(B10:D10,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.7</v>
       </c>
       <c r="G10">
-        <f>F10/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="19">
         <v>29.7</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="19">
         <v>30</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="19">
         <v>30</v>
       </c>
-      <c r="E11" s="21">
-        <f t="shared" si="0"/>
+      <c r="E11" s="20">
+        <f t="shared" si="2"/>
         <v>89.7</v>
       </c>
       <c r="F11">
-        <f>E11/COUNTIF(B11:D11,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.900000000000002</v>
       </c>
       <c r="G11">
-        <f>F11/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9666666666666668</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -2579,24 +2387,15 @@
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
       <c r="H20" s="17"/>
-      <c r="F20">
-        <f>E20/COUNTIF(B20:D20,"&lt;&gt;0")</f>
-      </c>
-      <c r="G20">
-        <f>F20/3</f>
-      </c>
-    </row>
-    <row r="33" s="16" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="34" s="16" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="35" s="16" customFormat="1" x14ac:dyDescent="0.2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7879C3F-1CD0-47E3-9363-D407E7B2DA51}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="34.83203125" defaultRowHeight="18.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.1640625" style="16" bestFit="1" customWidth="1"/>
@@ -2633,240 +2432,260 @@
       <c r="A2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="19">
         <v>29.7</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="19">
         <v>29.8</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="19">
         <v>29.6</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="20">
         <f>SUM(B2:D2)</f>
         <v>89.1</v>
       </c>
       <c r="F2">
-        <f>E2/COUNTIF(B2:D2,"&lt;&gt;0")</f>
+        <f t="shared" ref="F2:F11" si="0">E2/COUNTIF(B2:D2,"&lt;&gt;0")</f>
+        <v>29.7</v>
       </c>
       <c r="G2">
-        <f>F2/3</f>
+        <f t="shared" ref="G2:G11" si="1">F2/3</f>
+        <v>9.9</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <v>29.5</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="19">
         <v>29.5</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="19">
         <v>29.6</v>
       </c>
-      <c r="E3" s="21">
-        <f t="shared" ref="E3:E11" si="0">SUM(B3:D3)</f>
+      <c r="E3" s="20">
+        <f t="shared" ref="E3:E11" si="2">SUM(B3:D3)</f>
         <v>88.6</v>
       </c>
       <c r="F3">
-        <f>E3/COUNTIF(B3:D3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.533333333333331</v>
       </c>
       <c r="G3">
-        <f>F3/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8444444444444432</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="19">
         <v>28.8</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="19">
         <v>28.6</v>
       </c>
-      <c r="E4" s="21">
-        <f t="shared" si="0"/>
+      <c r="E4" s="20">
+        <f t="shared" si="2"/>
         <v>57.400000000000006</v>
       </c>
       <c r="F4">
-        <f>E4/COUNTIF(B4:D4,"&lt;&gt;0")</f>
+        <f>E4/2</f>
+        <v>28.700000000000003</v>
       </c>
       <c r="G4">
-        <f>F4/3</f>
+        <f t="shared" si="1"/>
+        <v>9.5666666666666682</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="19">
         <v>30</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="19">
         <v>29.6</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="19">
         <v>29.9</v>
       </c>
-      <c r="E5" s="21">
-        <f t="shared" si="0"/>
+      <c r="E5" s="20">
+        <f t="shared" si="2"/>
         <v>89.5</v>
       </c>
       <c r="F5">
-        <f>E5/COUNTIF(B5:D5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.833333333333332</v>
       </c>
       <c r="G5">
-        <f>F5/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9444444444444446</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="19">
         <v>29.1</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="19">
         <v>29.7</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="19">
         <v>29.1</v>
       </c>
-      <c r="E6" s="21">
-        <f t="shared" si="0"/>
+      <c r="E6" s="20">
+        <f t="shared" si="2"/>
         <v>87.9</v>
       </c>
       <c r="F6">
-        <f>E6/COUNTIF(B6:D6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.3</v>
       </c>
       <c r="G6">
-        <f>F6/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7666666666666675</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="19">
         <v>30</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="19">
         <v>30</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="19">
         <v>29.9</v>
       </c>
-      <c r="E7" s="21">
-        <f t="shared" si="0"/>
+      <c r="E7" s="20">
+        <f t="shared" si="2"/>
         <v>89.9</v>
       </c>
       <c r="F7">
-        <f>E7/COUNTIF(B7:D7,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.966666666666669</v>
       </c>
       <c r="G7">
-        <f>F7/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9888888888888889</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="19">
         <v>29.3</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="22">
         <v>29.3</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="19">
         <v>29</v>
       </c>
-      <c r="E8" s="21">
-        <f t="shared" si="0"/>
+      <c r="E8" s="20">
+        <f t="shared" si="2"/>
         <v>87.6</v>
       </c>
       <c r="F8">
-        <f>E8/COUNTIF(B8:D8,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.2</v>
       </c>
       <c r="G8">
-        <f>F8/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7333333333333325</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="19">
         <v>29.3</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="19">
         <v>29.4</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="19">
         <v>29.2</v>
       </c>
-      <c r="E9" s="21">
-        <f t="shared" si="0"/>
+      <c r="E9" s="20">
+        <f t="shared" si="2"/>
         <v>87.9</v>
       </c>
       <c r="F9">
-        <f>E9/COUNTIF(B9:D9,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.3</v>
       </c>
       <c r="G9">
-        <f>F9/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7666666666666675</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="19">
         <v>29.6</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="19">
         <v>29.6</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="19">
         <v>29.7</v>
       </c>
-      <c r="E10" s="21">
-        <f t="shared" si="0"/>
+      <c r="E10" s="20">
+        <f t="shared" si="2"/>
         <v>88.9</v>
       </c>
       <c r="F10">
-        <f>E10/COUNTIF(B10:D10,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.633333333333336</v>
       </c>
       <c r="G10">
-        <f>F10/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8777777777777782</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="19">
         <v>29.5</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="19">
         <v>29.4</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="19">
         <v>29.9</v>
       </c>
-      <c r="E11" s="21">
-        <f t="shared" si="0"/>
+      <c r="E11" s="20">
+        <f t="shared" si="2"/>
         <v>88.8</v>
       </c>
       <c r="F11">
-        <f>E11/COUNTIF(B11:D11,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.599999999999998</v>
       </c>
       <c r="G11">
-        <f>F11/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8666666666666654</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -2878,24 +2697,15 @@
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
       <c r="H20" s="17"/>
-      <c r="F20">
-        <f>E20/COUNTIF(B20:D20,"&lt;&gt;0")</f>
-      </c>
-      <c r="G20">
-        <f>F20/3</f>
-      </c>
-    </row>
-    <row r="33" s="16" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="34" s="16" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="35" s="16" customFormat="1" x14ac:dyDescent="0.2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FB18CC4-3422-43F0-8813-7562712E2ABC}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="34.83203125" defaultRowHeight="18.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.1640625" style="16" bestFit="1" customWidth="1"/>
@@ -2932,240 +2742,260 @@
       <c r="A2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="19">
         <v>30</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="19">
         <v>30</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="19">
         <v>29.8</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="20">
         <f>SUM(B2:D2)</f>
         <v>89.8</v>
       </c>
       <c r="F2">
-        <f>E2/COUNTIF(B2:D2,"&lt;&gt;0")</f>
+        <f t="shared" ref="F2:F11" si="0">E2/COUNTIF(B2:D2,"&lt;&gt;0")</f>
+        <v>29.933333333333334</v>
       </c>
       <c r="G2">
-        <f>F2/3</f>
+        <f t="shared" ref="G2:G11" si="1">F2/3</f>
+        <v>9.9777777777777779</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <v>30</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="19">
         <v>29.7</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="19">
         <v>30</v>
       </c>
-      <c r="E3" s="21">
-        <f t="shared" ref="E3:E11" si="0">SUM(B3:D3)</f>
+      <c r="E3" s="20">
+        <f t="shared" ref="E3:E11" si="2">SUM(B3:D3)</f>
         <v>89.7</v>
       </c>
       <c r="F3">
-        <f>E3/COUNTIF(B3:D3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.900000000000002</v>
       </c>
       <c r="G3">
-        <f>F3/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9666666666666668</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="19">
         <v>29.7</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="19">
         <v>29.4</v>
       </c>
-      <c r="E4" s="21">
-        <f t="shared" si="0"/>
+      <c r="E4" s="20">
+        <f t="shared" si="2"/>
         <v>59.099999999999994</v>
       </c>
       <c r="F4">
-        <f>E4/COUNTIF(B4:D4,"&lt;&gt;0")</f>
+        <f>E4/2</f>
+        <v>29.549999999999997</v>
       </c>
       <c r="G4">
-        <f>F4/3</f>
+        <f t="shared" si="1"/>
+        <v>9.85</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="19">
         <v>30</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="19">
         <v>30</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="19">
         <v>30</v>
       </c>
-      <c r="E5" s="21">
-        <f t="shared" si="0"/>
+      <c r="E5" s="20">
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="F5">
-        <f>E5/COUNTIF(B5:D5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="G5">
-        <f>F5/3</f>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="19">
         <v>30</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="19">
         <v>29.9</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="19">
         <v>29.9</v>
       </c>
-      <c r="E6" s="21">
-        <f t="shared" si="0"/>
+      <c r="E6" s="20">
+        <f t="shared" si="2"/>
         <v>89.8</v>
       </c>
       <c r="F6">
-        <f>E6/COUNTIF(B6:D6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.933333333333334</v>
       </c>
       <c r="G6">
-        <f>F6/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9777777777777779</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="19">
         <v>29.9</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="19">
         <v>29.9</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="19">
         <v>29.1</v>
       </c>
-      <c r="E7" s="21">
-        <f t="shared" si="0"/>
+      <c r="E7" s="20">
+        <f t="shared" si="2"/>
         <v>88.9</v>
       </c>
       <c r="F7">
-        <f>E7/COUNTIF(B7:D7,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.633333333333336</v>
       </c>
       <c r="G7">
-        <f>F7/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8777777777777782</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="19">
         <v>30</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="22">
         <v>30</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="19">
         <v>29.6</v>
       </c>
-      <c r="E8" s="21">
-        <f t="shared" si="0"/>
+      <c r="E8" s="20">
+        <f t="shared" si="2"/>
         <v>89.6</v>
       </c>
       <c r="F8">
-        <f>E8/COUNTIF(B8:D8,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.866666666666664</v>
       </c>
       <c r="G8">
-        <f>F8/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9555555555555539</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="19">
         <v>29.8</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="19">
         <v>29.7</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="19">
         <v>29.7</v>
       </c>
-      <c r="E9" s="21">
-        <f t="shared" si="0"/>
+      <c r="E9" s="20">
+        <f t="shared" si="2"/>
         <v>89.2</v>
       </c>
       <c r="F9">
-        <f>E9/COUNTIF(B9:D9,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.733333333333334</v>
       </c>
       <c r="G9">
-        <f>F9/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9111111111111114</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="19">
         <v>29.8</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="19">
         <v>29.9</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="19">
         <v>29.6</v>
       </c>
-      <c r="E10" s="21">
-        <f t="shared" si="0"/>
+      <c r="E10" s="20">
+        <f t="shared" si="2"/>
         <v>89.300000000000011</v>
       </c>
       <c r="F10">
-        <f>E10/COUNTIF(B10:D10,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.766666666666669</v>
       </c>
       <c r="G10">
-        <f>F10/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9222222222222225</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="19">
         <v>30</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="19">
         <v>29.9</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="19">
         <v>30</v>
       </c>
-      <c r="E11" s="21">
-        <f t="shared" si="0"/>
+      <c r="E11" s="20">
+        <f t="shared" si="2"/>
         <v>89.9</v>
       </c>
       <c r="F11">
-        <f>E11/COUNTIF(B11:D11,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.966666666666669</v>
       </c>
       <c r="G11">
-        <f>F11/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9888888888888889</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -3177,16 +3007,7 @@
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
       <c r="H20" s="17"/>
-      <c r="F20">
-        <f>E20/COUNTIF(B20:D20,"&lt;&gt;0")</f>
-      </c>
-      <c r="G20">
-        <f>F20/3</f>
-      </c>
-    </row>
-    <row r="33" s="16" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="34" s="16" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="35" s="16" customFormat="1" x14ac:dyDescent="0.2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
